--- a/plugins/osi-finance/assets/templates/支払管理台帳_テンプレート.xlsx
+++ b/plugins/osi-finance/assets/templates/支払管理台帳_テンプレート.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_使い方" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_使い方_支払管理台帳" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支払先マスタ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次支払管理" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="経費一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="源泉徴収管理" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次支払スケジュール" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,15 +32,13 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -47,16 +47,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -64,33 +59,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,61 +438,103 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="140" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>支払管理台帳テンプレート（AP・払う側）  ※OSI Finance</t>
+          <t>支払管理台帳 テンプレート（AP・払う側）  ※OSI Finance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>・ファイル名は『支払管理台帳.xlsx』（または settings の LEDGER_PAYMENT_FILE）にして置きます。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>・自組織の Drive `31.請求管理/01.受領請求書/` に『支払管理台帳.xlsx』として配置します。</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>・置き場所：経理フォルダ（osi-profile.md の paths.finance ＝ 拡張の設定「台帳フォルダ」xlsx_ledger_dir）。共通マスタ・請求管理台帳・支払管理台帳・仕訳台帳・コンソールを開く.html を同じフォルダに置く。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>・黄色＝記入例。実運用前に削除。</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>・データ行は空です。記入例は下にだけ書いてあります（台帳の行に例を置くと、月初の請求処理などが本物として拾います）。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>・支払先マスタ＝支払先の正本（既定の支払方法で 振込/カード を振り分け）。</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>・列はヘッダー名で読みます。列の追加・並べ替えはかまいませんが、列名は変えないでください。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>・月次支払管理＝受領請求書由来の支払予定/支払済。経費一覧＝請求書を伴わない経費。</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>・分からない値は空欄にして、理由を備考に書きます（「要確認」などの文字で埋めない）。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>・カード払い(自動課金SaaS等)は台帳に起票せずカード連携任せ＝二重計上防止。証憑は 32.経費管理 へ。</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>・仕様の正本：プラグインの assets/schema/data-layout.yaml。テンプレートは assets/scripts/build_templates.py で生成。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>・請求書ID = 支払先ID + 対象月(YYYYMM) + 請求書番号。摘要に入れてMF突合キーにする。</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>・見出し行の位置は仕様どおりです：支払先マスタ・経費一覧・源泉徴収管理は3行目、月次支払管理は4行目、月次支払スケジュールは1行目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>・支払先マスタ：振込先口座・源泉の要否・支払サイクル。会社の名前は 取引先ID で共通マスタの取引先マスタを引きます。既定の支払方法で 振込／カード を振り分けます（カード払いは支払予定に起票しない＝二重払い防止）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>・月次支払管理＝支払の実績。月次支払スケジュール＝契約から展開した支払の予定。経費一覧＝明細の蓄積（ここから仕訳を起こさない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>・源泉徴収管理：源泉対象の支払の税額と納付状況。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>記入例（参考。台帳には書かない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  支払先マスタ：支払先ID=V-001 / 支払先名=サンプル株式会社 / 支払先区分=法人 / 支払カテゴリ=外注費 / 取引先ID=P-001 / 既定の支払方法=振込 / 源泉徴収対象=なし / ステータス=支払対象</t>
         </is>
       </c>
     </row>
@@ -525,202 +549,200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A2:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" style="3" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" style="3" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>凡例：支払先マスタ。見出しは3行目。列の意味は「00_使い方_支払管理台帳」タブを参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>支払先ID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>正式名称</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>既定支払方法</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>既定勘定科目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>既定税区分(MF)</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>インボイス登録番号</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>支払先名</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>支払先区分</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>支払カテゴリ</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>主担当者名</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>メールアドレス</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>振込先銀行</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>支店</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>預金種別</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>振込先支店</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>口座種別</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>口座番号</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>口座名義</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>源泉対象</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>V-001</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>（記入例）サンプル開発</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>振込</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>業務委託料</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>課税仕入10%</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>T0000000000000</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>○○銀行</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>○○支店</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>0000000</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>サンプルカイハツ</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>記入例。実運用前に削除</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>V-002</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>（記入例）国外SaaS</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>カード</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>通信費</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>対象外(国外SaaS)</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>カード払い＝台帳起票しない(連携任せ)</t>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>契約開始日</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>契約終了日</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>契約タイプ</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>月額固定（税抜）</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>時間単価（税抜）</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>消費税率</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>源泉徴収対象</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>源泉徴収税率</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>支払サイクル</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>取引先ID</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>作成者</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>更新者</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>既定の支払方法</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="5">
+    <dataValidation sqref="C4:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+      <formula1>"法人,個人,個人事業主,要確認"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N4:N2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+      <formula1>"月額固定,都度"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q4:Q2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+      <formula1>"10.0%,0.0%,非課税,対象外（不課税）"</formula1>
+    </dataValidation>
+    <dataValidation sqref="V4:V2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+      <formula1>"支払対象,要確認"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AA4:AA2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+      <formula1>"振込,カード,口座振替,現金,カード発行会社"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -731,178 +753,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A4:AB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" style="3" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" style="3" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>請求書ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>支払先ID</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>支払先名</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>支払カテゴリ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>対象月</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>勘定科目</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>税区分(MF)</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>金額(税抜)</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>契約タイプ</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>月額固定（税抜）</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>稼働時間</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>時間単価額（税抜）</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>実費・その他（税抜）</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>支払金額（税抜）</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>消費税額</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>金額(税込)</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>源泉徴収税額</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>振込額</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>支払金額（税込）</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>請求書番号</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>請求書受領日</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>支払予定日</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>支払日</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>MF連携状態</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>MF仕訳ID</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>請求書ファイル</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>V-001-202604-INV1001</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>V-001</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>（記入例）サンプル開発</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>業務委託料</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>課税仕入10%</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>550000</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>550000</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>支払済</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>未連携</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>01.受領請求書/2026-04/サンプル開発_INV1001.pdf</t>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>支払額</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>差額</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>支払ステータス</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>遅延日数</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>承認者</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>作成者</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>更新者</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>支払方法</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="C5:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+      <formula1>"外注費,経費,その他"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T5:T2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+      <formula1>"未払い,支払済"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AB5:AB2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+      <formula1>"振込,カード,口座振替,現金"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -913,134 +950,318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A2:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" style="3" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="10" customWidth="1" style="3" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>凡例：経費一覧。見出しは3行目。列の意味は「00_使い方_支払管理台帳」タブを参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>支払先ID</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>費目</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>発生月</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>発生日</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>金額（税抜）</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>消費税額</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>金額（税込）</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>作成者</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>更新者</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:L3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" style="3" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>凡例：源泉徴収管理。見出しは3行目。列の意味は「00_使い方_支払管理台帳」タブを参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>支払先ID</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>支払先名</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>支払先区分</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>対象月</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>支払金額（税抜）</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>源泉徴収税率</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>源泉徴収税額</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>差引支払額</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>納付期限</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>納付日</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>納付ステータス</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12" customWidth="1" style="3" min="2" max="2"/>
+    <col width="14" customWidth="1" style="3" min="3" max="3"/>
+    <col width="14" customWidth="1" style="3" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" style="3" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" style="3" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>経費ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>予定ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>契約ID</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>取引先ID</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>支払先ID</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>発生日</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>勘定科目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>税区分(MF)</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>金額(税抜)</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>消費税額</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>金額(税込)</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>支払先名</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>対象月</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>予定額(税込)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>支払予定日</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>MF連携状態</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>MF仕訳ID</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>E-001</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>会議費</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>課税仕入10%</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>5500</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>支払済</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>未連携</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>記入例。実運用前に削除</t>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>受領請求書ID</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>突合結果</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>突合日時</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>作成者</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>更新者</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>更新日時</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="I2:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+      <formula1>"未払予定,請求書受領済,支払済"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+      <formula1>"一致,未計上"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/plugins/osi-finance/assets/templates/支払管理台帳_テンプレート.xlsx
+++ b/plugins/osi-finance/assets/templates/支払管理台帳_テンプレート.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -510,31 +510,38 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>・月次支払管理＝支払の実績。月次支払スケジュール＝契約から展開した支払の予定。経費一覧＝明細の蓄積（ここから仕訳を起こさない）。</t>
+          <t>・受領請求書を月次支払管理に起票するときは 受領請求書ファイル（01.受領請求書/YYYY-MM/…pdf）を必ず書きます。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>・月次支払管理＝支払の実績。月次支払スケジュール＝契約から展開した支払の予定。経費一覧＝明細の蓄積（ここから仕訳を起こさない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>・源泉徴収管理：源泉対象の支払の税額と納付状況。</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n"/>
-    </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>記入例（参考。台帳には書かない）</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支払先マスタ：支払先ID=V-001 / 支払先名=サンプル株式会社 / 支払先区分=法人 / 支払カテゴリ=外注費 / 取引先ID=P-001 / 既定の支払方法=振込 / 源泉徴収対象=なし / ステータス=支払対象</t>
+          <t>記入例（参考。台帳には書かない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  支払先マスタ：支払先ID=V-001 / 支払カテゴリ=外注費 / 取引先ID=P-001 / 既定の支払方法=振込 / 源泉徴収対象=なし / ステータス=支払対象</t>
         </is>
       </c>
     </row>
@@ -549,36 +556,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AA3"/>
+  <dimension ref="A2:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="3" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" style="3" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" style="3" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" style="3" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" style="3" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -596,130 +601,120 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>支払先名</t>
+          <t>支払先区分</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>支払先区分</t>
+          <t>支払カテゴリ</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>支払カテゴリ</t>
+          <t>メールアドレス</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>主担当者名</t>
+          <t>振込先銀行</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>メールアドレス</t>
+          <t>振込先支店</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>振込先銀行</t>
+          <t>口座種別</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>振込先支店</t>
+          <t>口座番号</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>口座種別</t>
+          <t>口座名義</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>口座番号</t>
+          <t>契約開始日</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>口座名義</t>
+          <t>契約終了日</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>契約開始日</t>
+          <t>契約タイプ</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>契約終了日</t>
+          <t>月額固定（税抜）</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>契約タイプ</t>
+          <t>時間単価（税抜）</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>月額固定（税抜）</t>
+          <t>消費税率</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>時間単価（税抜）</t>
+          <t>源泉徴収対象</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>消費税率</t>
+          <t>源泉徴収税率</t>
         </is>
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>源泉徴収対象</t>
+          <t>支払サイクル</t>
         </is>
       </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
-          <t>源泉徴収税率</t>
+          <t>取引先ID</t>
         </is>
       </c>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>支払サイクル</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="U3" s="4" t="inlineStr">
         <is>
-          <t>取引先ID</t>
+          <t>作成者</t>
         </is>
       </c>
       <c r="V3" s="4" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="W3" s="4" t="inlineStr">
         <is>
-          <t>作成者</t>
+          <t>更新者</t>
         </is>
       </c>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>更新日時</t>
         </is>
       </c>
       <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>更新者</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>更新日時</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>既定の支払方法</t>
         </is>
@@ -727,19 +722,19 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="C4:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+    <dataValidation sqref="B4:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
       <formula1>"法人,個人,個人事業主,要確認"</formula1>
     </dataValidation>
-    <dataValidation sqref="N4:N2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+    <dataValidation sqref="L4:L2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
       <formula1>"月額固定,都度"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q4:Q2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+    <dataValidation sqref="O4:O2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
       <formula1>"10.0%,0.0%,非課税,対象外（不課税）"</formula1>
     </dataValidation>
-    <dataValidation sqref="V4:V2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+    <dataValidation sqref="T4:T2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
       <formula1>"支払対象,要確認"</formula1>
     </dataValidation>
-    <dataValidation sqref="AA4:AA2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+    <dataValidation sqref="Y4:Y2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
       <formula1>"振込,カード,口座振替,現金,カード発行会社"</formula1>
     </dataValidation>
   </dataValidations>
@@ -753,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:AB4"/>
+  <dimension ref="A4:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="3" min="1" max="1"/>
@@ -784,6 +779,9 @@
     <col width="10" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="4">
@@ -927,9 +925,24 @@
           <t>支払方法</t>
         </is>
       </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>突合結果</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>突合日時</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>受領請求書ファイル</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="C5:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
       <formula1>"外注費,経費,その他"</formula1>
     </dataValidation>
@@ -938,6 +951,9 @@
     </dataValidation>
     <dataValidation sqref="AB5:AB2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
       <formula1>"振込,カード,口座振替,現金"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AC5:AC2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="仕様外の値" error="data-layout.yaml の values 以外の値です" type="list" errorStyle="warning">
+      <formula1>"一致,未計上"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
